--- a/server/templates/employee-temporary-template.xlsx
+++ b/server/templates/employee-temporary-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Documents\projects\nanafruit-hrm\server\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1607C8D9-B613-4643-9871-BBED693BD59F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02012FBB-6F5A-4050-A545-B4DC30A416C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
   <si>
     <t>ชื่อเล่น</t>
   </si>
@@ -249,6 +249,18 @@
   </si>
   <si>
     <t>TEMP-EMP-IMP</t>
+  </si>
+  <si>
+    <t>หัวหน้างาน</t>
+  </si>
+  <si>
+    <t>EMPCODE001</t>
+  </si>
+  <si>
+    <t>กลุ่ม OT</t>
+  </si>
+  <si>
+    <t>Daily Temporary</t>
   </si>
 </sst>
 </file>
@@ -671,7 +683,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:Q3"/>
   <sheetFormatPr defaultRowHeight="24" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="16.5703125" style="2" customWidth="1"/>
@@ -682,21 +694,21 @@
     <col min="6" max="6" width="11.42578125" style="2" customWidth="1"/>
     <col min="7" max="7" width="19.7109375" style="2" customWidth="1"/>
     <col min="8" max="8" width="20.28515625" style="2" customWidth="1"/>
-    <col min="9" max="10" width="17.28515625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="21.140625" style="2" customWidth="1"/>
-    <col min="12" max="12" width="16.5703125" style="2" customWidth="1"/>
-    <col min="13" max="13" width="19.85546875" style="2" customWidth="1"/>
-    <col min="14" max="14" width="20.140625" style="2" customWidth="1"/>
-    <col min="15" max="15" width="13.85546875" style="2" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="2"/>
+    <col min="9" max="11" width="17.28515625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="21.140625" style="2" customWidth="1"/>
+    <col min="13" max="13" width="16.5703125" style="2" customWidth="1"/>
+    <col min="14" max="14" width="19.85546875" style="2" customWidth="1"/>
+    <col min="15" max="16" width="20.140625" style="2" customWidth="1"/>
+    <col min="17" max="17" width="13.85546875" style="2" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:15" s="5" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="7" t="s">
         <v>25</v>
       </c>
@@ -728,22 +740,28 @@
         <v>20</v>
       </c>
       <c r="K2" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="L2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="L2" s="7" t="s">
+      <c r="M2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="M2" s="7" t="s">
+      <c r="N2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="N2" s="7" t="s">
+      <c r="O2" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="O2" s="7" t="s">
+      <c r="P2" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q2" s="7" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
@@ -775,18 +793,24 @@
         <v>21</v>
       </c>
       <c r="K3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="M3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="N3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="O3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="O3" s="1">
+      <c r="P3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q3" s="1">
         <v>350</v>
       </c>
     </row>

--- a/server/templates/employee-temporary-template.xlsx
+++ b/server/templates/employee-temporary-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Documents\projects\nanafruit-hrm\server\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02012FBB-6F5A-4050-A545-B4DC30A416C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93483148-BB29-4DDF-9A71-24D884BB1A2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="35">
   <si>
     <t>ชื่อเล่น</t>
   </si>
@@ -261,6 +261,18 @@
   </si>
   <si>
     <t>Daily Temporary</t>
+  </si>
+  <si>
+    <t>สัญชาติ</t>
+  </si>
+  <si>
+    <t>ไทย</t>
+  </si>
+  <si>
+    <t>1234567890121</t>
+  </si>
+  <si>
+    <t>เลขบัตรประชาชน</t>
   </si>
 </sst>
 </file>
@@ -350,7 +362,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -367,6 +379,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -683,32 +702,33 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="24" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="16.5703125" style="2" customWidth="1"/>
     <col min="2" max="2" width="13.85546875" style="2" customWidth="1"/>
     <col min="3" max="3" width="16.5703125" style="2" customWidth="1"/>
     <col min="4" max="4" width="25.28515625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="16.28515625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="11.42578125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="19.7109375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="20.28515625" style="2" customWidth="1"/>
-    <col min="9" max="11" width="17.28515625" style="2" customWidth="1"/>
-    <col min="12" max="12" width="21.140625" style="2" customWidth="1"/>
-    <col min="13" max="13" width="16.5703125" style="2" customWidth="1"/>
-    <col min="14" max="14" width="19.85546875" style="2" customWidth="1"/>
-    <col min="15" max="16" width="20.140625" style="2" customWidth="1"/>
-    <col min="17" max="17" width="13.85546875" style="2" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="2"/>
+    <col min="5" max="6" width="16.28515625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="29.140625" style="8" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="19.7109375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="20.28515625" style="2" customWidth="1"/>
+    <col min="11" max="13" width="17.28515625" style="2" customWidth="1"/>
+    <col min="14" max="14" width="21.140625" style="2" customWidth="1"/>
+    <col min="15" max="15" width="16.5703125" style="2" customWidth="1"/>
+    <col min="16" max="16" width="19.85546875" style="2" customWidth="1"/>
+    <col min="17" max="18" width="20.140625" style="2" customWidth="1"/>
+    <col min="19" max="19" width="13.85546875" style="2" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:17" s="5" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="7" t="s">
         <v>25</v>
       </c>
@@ -725,43 +745,49 @@
         <v>0</v>
       </c>
       <c r="F2" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="H2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="I2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="J2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="K2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="L2" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="K2" s="7" t="s">
+      <c r="M2" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="L2" s="7" t="s">
+      <c r="N2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="M2" s="7" t="s">
+      <c r="O2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="N2" s="7" t="s">
+      <c r="P2" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="O2" s="7" t="s">
+      <c r="Q2" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="P2" s="7" t="s">
+      <c r="R2" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="Q2" s="7" t="s">
+      <c r="S2" s="7" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
@@ -778,39 +804,45 @@
         <v>14</v>
       </c>
       <c r="F3" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="4">
+      <c r="I3" s="4">
         <v>46235</v>
       </c>
-      <c r="H3" s="4">
+      <c r="J3" s="4">
         <v>46235</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="K3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="L3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="M3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="N3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="O3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="P3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="O3" s="3" t="s">
+      <c r="Q3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="P3" s="3" t="s">
+      <c r="R3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="Q3" s="1">
+      <c r="S3" s="1">
         <v>350</v>
       </c>
     </row>
